--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$82</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$85</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$78</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4385,7 +4385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.1, "op_wape_pct": 25.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 417.38, "rev_act": 645.61, "op_pred": 71.11, "op_act": 117.31}, {"q": "2025Q4", "rev_pred": 535.38, "rev_act": 593.01, "op_pred": 91.21, "op_act": 87.1}, {"q": "2026Q1", "rev_pred": 585.66, "rev_act": 591.37, "op_pred": 99.77, "op_act": 65.69}, {"q": "2026Q2", "rev_pred": 534.26, "rev_act": 641.32, "op_pred": 91.02, "op_act": 100.07}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 16.1, "op_wape_pct": 25.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 417.38, "rev_act": 645.61, "op_pred": 71.11, "op_act": 117.31}, {"q": "2025Q4", "rev_pred": 535.38, "rev_act": 593.01, "op_pred": 91.21, "op_act": 87.1}, {"q": "2026Q1", "rev_pred": 585.66, "rev_act": 591.37, "op_pred": 99.77, "op_act": 65.69}, {"q": "2026Q2", "rev_pred": 534.26, "rev_act": 641.32, "op_pred": 91.02, "op_act": 100.07}]}</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO82"/>
+  <dimension ref="A1:AO85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15809,78 +15809,33 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>-16250.24</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F64" s="9" t="n"/>
-      <c r="G64" s="18" t="n">
-        <v>-5295.24</v>
-      </c>
-      <c r="H64" s="18" t="n">
-        <v>2543.66</v>
-      </c>
-      <c r="I64" s="18" t="n">
-        <v>2923.94</v>
-      </c>
-      <c r="J64" s="18" t="n">
-        <v>21252.31</v>
-      </c>
-      <c r="K64" s="34" t="n">
-        <v>21424.67</v>
-      </c>
-      <c r="L64" s="18" t="n">
-        <v>10439.1</v>
-      </c>
-      <c r="M64" s="18" t="n">
-        <v>8760.879999999999</v>
-      </c>
-      <c r="N64" s="18" t="n">
-        <v>15731.5</v>
-      </c>
-      <c r="O64" s="18" t="n">
-        <v>615.04</v>
-      </c>
-      <c r="P64" s="34" t="n">
-        <v>35546.52</v>
-      </c>
-      <c r="Q64" s="18" t="n">
-        <v>11011.04</v>
-      </c>
-      <c r="R64" s="18" t="n">
-        <v>21662.2</v>
-      </c>
-      <c r="S64" s="18" t="n">
-        <v>3151.76</v>
-      </c>
-      <c r="T64" s="18" t="n">
-        <v>-7319.64</v>
-      </c>
-      <c r="U64" s="34" t="n">
-        <v>28505.36</v>
-      </c>
+      <c r="K64" s="9" t="n"/>
+      <c r="P64" s="9" t="n"/>
+      <c r="U64" s="9" t="n"/>
       <c r="V64" s="18" t="n">
-        <v>-5965.08</v>
+        <v>790.34</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>4800.69</v>
+        <v>696.9400000000001</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>19575.3</v>
+        <v>675.01</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>19469.11</v>
+        <v>839.49</v>
       </c>
       <c r="Z64" s="34" t="n">
-        <v>37880.02</v>
+        <v>3001.78</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>4911.75</v>
+        <v>844.49</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>2577.36</v>
+        <v>828.62</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -15902,78 +15857,33 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E65" s="18" t="n">
-        <v>90.95999999999999</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F65" s="9" t="n"/>
-      <c r="G65" s="18" t="n">
-        <v>93.76000000000001</v>
-      </c>
-      <c r="H65" s="18" t="n">
-        <v>103.72</v>
-      </c>
-      <c r="I65" s="18" t="n">
-        <v>232.47</v>
-      </c>
-      <c r="J65" s="18" t="n">
-        <v>434.78</v>
-      </c>
-      <c r="K65" s="34" t="n">
-        <v>864.73</v>
-      </c>
-      <c r="L65" s="18" t="n">
-        <v>675.8</v>
-      </c>
-      <c r="M65" s="18" t="n">
-        <v>761.5599999999999</v>
-      </c>
-      <c r="N65" s="18" t="n">
-        <v>971.26</v>
-      </c>
-      <c r="O65" s="18" t="n">
-        <v>1026.7</v>
-      </c>
-      <c r="P65" s="34" t="n">
-        <v>3435.32</v>
-      </c>
-      <c r="Q65" s="18" t="n">
-        <v>798.5599999999999</v>
-      </c>
-      <c r="R65" s="18" t="n">
-        <v>1056.19</v>
-      </c>
-      <c r="S65" s="18" t="n">
-        <v>670.62</v>
-      </c>
-      <c r="T65" s="18" t="n">
-        <v>1331.74</v>
-      </c>
-      <c r="U65" s="34" t="n">
-        <v>3857.11</v>
-      </c>
+      <c r="K65" s="9" t="n"/>
+      <c r="P65" s="9" t="n"/>
+      <c r="U65" s="9" t="n"/>
       <c r="V65" s="18" t="n">
-        <v>1012.35</v>
+        <v>15.88</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>755.9400000000001</v>
+        <v>12.43</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>520.51</v>
+        <v>10.37</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>856.33</v>
+        <v>10.23</v>
       </c>
       <c r="Z65" s="34" t="n">
-        <v>3145.13</v>
+        <v>48.91</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>538.3200000000001</v>
+        <v>10.01</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>806.55</v>
+        <v>11.22</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -15995,78 +15905,33 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E66" s="18" t="n">
-        <v>-24.1</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F66" s="9" t="n"/>
-      <c r="G66" s="18" t="n">
-        <v>-35.1</v>
-      </c>
-      <c r="H66" s="18" t="n">
-        <v>359.51</v>
-      </c>
-      <c r="I66" s="18" t="n">
-        <v>-55.76</v>
-      </c>
-      <c r="J66" s="18" t="n">
-        <v>-81.88</v>
-      </c>
-      <c r="K66" s="34" t="n">
-        <v>186.77</v>
-      </c>
-      <c r="L66" s="18" t="n">
-        <v>-4137.89</v>
-      </c>
-      <c r="M66" s="18" t="n">
-        <v>-5008</v>
-      </c>
-      <c r="N66" s="18" t="n">
-        <v>-1575.96</v>
-      </c>
-      <c r="O66" s="18" t="n">
-        <v>-1571.86</v>
-      </c>
-      <c r="P66" s="34" t="n">
-        <v>-12293.71</v>
-      </c>
-      <c r="Q66" s="18" t="n">
-        <v>-165.74</v>
-      </c>
-      <c r="R66" s="18" t="n">
-        <v>-5851.77</v>
-      </c>
-      <c r="S66" s="18" t="n">
-        <v>-2318.62</v>
-      </c>
-      <c r="T66" s="18" t="n">
-        <v>-2146.05</v>
-      </c>
-      <c r="U66" s="34" t="n">
-        <v>-10482.18</v>
-      </c>
+      <c r="K66" s="9" t="n"/>
+      <c r="P66" s="9" t="n"/>
+      <c r="U66" s="9" t="n"/>
       <c r="V66" s="18" t="n">
-        <v>-3423.95</v>
+        <v>774.46</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>-4375.55</v>
+        <v>684.51</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>-109.58</v>
+        <v>664.64</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>-4926.84</v>
+        <v>829.26</v>
       </c>
       <c r="Z66" s="34" t="n">
-        <v>-12835.92</v>
+        <v>2952.87</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>-1820.95</v>
+        <v>834.48</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>-2701.7</v>
+        <v>817.4</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -16088,78 +15953,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>2727.04</v>
+        <v>-16250.24</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>29878.6</v>
+        <v>-5295.24</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>2454.46</v>
+        <v>2543.66</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>8106.79</v>
+        <v>2923.94</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>1651.28</v>
+        <v>21252.31</v>
       </c>
       <c r="K67" s="34" t="n">
-        <v>42091.13</v>
+        <v>21424.67</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>1923.5</v>
+        <v>10439.1</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-8839.91</v>
+        <v>8760.879999999999</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-505.1</v>
+        <v>15731.5</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-26554.76</v>
+        <v>615.04</v>
       </c>
       <c r="P67" s="34" t="n">
-        <v>-33976.27</v>
+        <v>35546.52</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>-11857.63</v>
+        <v>11011.04</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>922.05</v>
+        <v>21662.2</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>-9248.74</v>
+        <v>3151.76</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>2832.59</v>
+        <v>-7319.64</v>
       </c>
       <c r="U67" s="34" t="n">
-        <v>-17351.73</v>
+        <v>28505.36</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>-2766.92</v>
+        <v>-5965.08</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>-6944.64</v>
+        <v>4800.69</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>-17248.61</v>
+        <v>19575.3</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>-13357.9</v>
+        <v>19469.11</v>
       </c>
       <c r="Z67" s="34" t="n">
-        <v>-40318.07</v>
+        <v>37880.02</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>1398.22</v>
+        <v>4911.75</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>4434.12</v>
+        <v>2577.36</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -16181,70 +16046,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>43.09</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="F68" s="9" t="n"/>
+      <c r="G68" s="18" t="n">
+        <v>93.76000000000001</v>
+      </c>
+      <c r="H68" s="18" t="n">
+        <v>103.72</v>
+      </c>
       <c r="I68" s="18" t="n">
-        <v>0</v>
+        <v>232.47</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="K68" s="9" t="n"/>
+        <v>434.78</v>
+      </c>
+      <c r="K68" s="34" t="n">
+        <v>864.73</v>
+      </c>
       <c r="L68" s="18" t="n">
-        <v>12.73</v>
+        <v>675.8</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>94.93000000000001</v>
+        <v>761.5599999999999</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>2.88</v>
+        <v>971.26</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>8.18</v>
+        <v>1026.7</v>
       </c>
       <c r="P68" s="34" t="n">
-        <v>118.72</v>
+        <v>3435.32</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>0</v>
+        <v>798.5599999999999</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>4.05</v>
+        <v>1056.19</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>0</v>
+        <v>670.62</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>0</v>
+        <v>1331.74</v>
       </c>
       <c r="U68" s="34" t="n">
-        <v>4.05</v>
+        <v>3857.11</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>27.82</v>
+        <v>1012.35</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>0</v>
+        <v>755.9400000000001</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>22.73</v>
+        <v>520.51</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>0</v>
+        <v>856.33</v>
       </c>
       <c r="Z68" s="34" t="n">
-        <v>50.55</v>
+        <v>3145.13</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>0</v>
+        <v>538.3200000000001</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>0</v>
+        <v>806.55</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -16266,78 +16139,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>1548.66</v>
+        <v>-24.1</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>60</v>
+        <v>-35.1</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>41.52</v>
+        <v>359.51</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>386.04</v>
+        <v>-55.76</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>471.24</v>
+        <v>-81.88</v>
       </c>
       <c r="K69" s="34" t="n">
-        <v>958.8</v>
+        <v>186.77</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>397.99</v>
+        <v>-4137.89</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>875.83</v>
+        <v>-5008</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>373.04</v>
+        <v>-1575.96</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>1018.16</v>
+        <v>-1571.86</v>
       </c>
       <c r="P69" s="34" t="n">
-        <v>2665.02</v>
+        <v>-12293.71</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>335.83</v>
+        <v>-165.74</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>805.54</v>
+        <v>-5851.77</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>1590.42</v>
+        <v>-2318.62</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>212.06</v>
+        <v>-2146.05</v>
       </c>
       <c r="U69" s="34" t="n">
-        <v>2943.85</v>
+        <v>-10482.18</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>449.94</v>
+        <v>-3423.95</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>312.82</v>
+        <v>-4375.55</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>3638.61</v>
+        <v>-109.58</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>70.31999999999999</v>
+        <v>-4926.84</v>
       </c>
       <c r="Z69" s="34" t="n">
-        <v>4471.69</v>
+        <v>-12835.92</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>0</v>
+        <v>-1820.95</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>70.73</v>
+        <v>-2701.7</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -16359,78 +16232,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>1548.66</v>
+        <v>2727.04</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>60</v>
+        <v>29878.6</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>41.52</v>
+        <v>2454.46</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>386.04</v>
+        <v>8106.79</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>509.54</v>
+        <v>1651.28</v>
       </c>
       <c r="K70" s="34" t="n">
-        <v>997.1</v>
+        <v>42091.13</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>406.39</v>
+        <v>1923.5</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>875.83</v>
+        <v>-8839.91</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>373.04</v>
+        <v>-505.1</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>1018.16</v>
+        <v>-26554.76</v>
       </c>
       <c r="P70" s="34" t="n">
-        <v>2673.42</v>
+        <v>-33976.27</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>335.83</v>
+        <v>-11857.63</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>805.54</v>
+        <v>922.05</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>1590.42</v>
+        <v>-9248.74</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>212.06</v>
+        <v>2832.59</v>
       </c>
       <c r="U70" s="34" t="n">
-        <v>2943.85</v>
+        <v>-17351.73</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>657.9400000000001</v>
+        <v>-2766.92</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>984.8200000000001</v>
+        <v>-6944.64</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>3742.11</v>
+        <v>-17248.61</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>70.31999999999999</v>
+        <v>-13357.9</v>
       </c>
       <c r="Z70" s="34" t="n">
-        <v>5455.19</v>
+        <v>-40318.07</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>0</v>
+        <v>1398.22</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>70.73</v>
+        <v>4434.12</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -16452,24 +16325,71 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0</v>
+        <v>43.09</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="I71" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="18" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="K71" s="9" t="n"/>
+      <c r="L71" s="18" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="M71" s="18" t="n">
+        <v>94.93000000000001</v>
+      </c>
+      <c r="N71" s="18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O71" s="18" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="P71" s="34" t="n">
+        <v>118.72</v>
+      </c>
+      <c r="Q71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K71" s="9" t="n"/>
-      <c r="P71" s="9" t="n"/>
-      <c r="U71" s="9" t="n"/>
-      <c r="Z71" s="9" t="n"/>
-      <c r="AB71" s="5" t="n"/>
+      <c r="R71" s="18" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="S71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V71" s="18" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="W71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="18" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="Y71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="34" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AA71" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
       <c r="AE71" s="11" t="n"/>
@@ -16490,78 +16410,78 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-140.97</v>
+        <v>1548.66</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>-20143.71</v>
+        <v>60</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-2866.12</v>
+        <v>41.52</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-72.56</v>
+        <v>386.04</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-71.97</v>
+        <v>471.24</v>
       </c>
       <c r="K72" s="34" t="n">
-        <v>-23154.36</v>
+        <v>958.8</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-74.09999999999999</v>
+        <v>397.99</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-872.29</v>
+        <v>875.83</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-90.48999999999999</v>
+        <v>373.04</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-94.73999999999999</v>
+        <v>1018.16</v>
       </c>
       <c r="P72" s="34" t="n">
-        <v>-1131.62</v>
+        <v>2665.02</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>-84.05</v>
+        <v>335.83</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>-4277.07</v>
+        <v>805.54</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>-17779.98</v>
+        <v>1590.42</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>-2360.87</v>
+        <v>212.06</v>
       </c>
       <c r="U72" s="34" t="n">
-        <v>-24501.97</v>
+        <v>2943.85</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>-88.95</v>
+        <v>449.94</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>-5397.8</v>
+        <v>312.82</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>577.76</v>
+        <v>3638.61</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>-10.23</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="Z72" s="34" t="n">
-        <v>-4919.22</v>
+        <v>4471.69</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>-10.01</v>
+        <v>0</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>-5322.69</v>
+        <v>70.73</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -16583,74 +16503,79 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0</v>
+        <v>1548.66</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="18" t="n">
-        <v>5000</v>
+        <v>60</v>
       </c>
       <c r="H73" s="18" t="n">
+        <v>41.52</v>
+      </c>
+      <c r="I73" s="18" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="J73" s="18" t="n">
+        <v>509.54</v>
+      </c>
+      <c r="K73" s="34" t="n">
+        <v>997.1</v>
+      </c>
+      <c r="L73" s="18" t="n">
+        <v>406.39</v>
+      </c>
+      <c r="M73" s="18" t="n">
+        <v>875.83</v>
+      </c>
+      <c r="N73" s="18" t="n">
+        <v>373.04</v>
+      </c>
+      <c r="O73" s="18" t="n">
+        <v>1018.16</v>
+      </c>
+      <c r="P73" s="34" t="n">
+        <v>2673.42</v>
+      </c>
+      <c r="Q73" s="18" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="R73" s="18" t="n">
+        <v>805.54</v>
+      </c>
+      <c r="S73" s="18" t="n">
+        <v>1590.42</v>
+      </c>
+      <c r="T73" s="18" t="n">
+        <v>212.06</v>
+      </c>
+      <c r="U73" s="34" t="n">
+        <v>2943.85</v>
+      </c>
+      <c r="V73" s="18" t="n">
+        <v>657.9400000000001</v>
+      </c>
+      <c r="W73" s="18" t="n">
+        <v>984.8200000000001</v>
+      </c>
+      <c r="X73" s="18" t="n">
+        <v>3742.11</v>
+      </c>
+      <c r="Y73" s="18" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="Z73" s="34" t="n">
+        <v>5455.19</v>
+      </c>
+      <c r="AA73" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="34" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N73" s="18" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="O73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" s="34" t="n">
-        <v>2124.99</v>
-      </c>
-      <c r="Q73" s="18" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="R73" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="S73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" s="34" t="n">
-        <v>2000.49</v>
-      </c>
-      <c r="V73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="5" t="n"/>
+      <c r="AB73" s="19" t="n">
+        <v>70.73</v>
+      </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
       <c r="AE73" s="11" t="n"/>
@@ -16671,73 +16596,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="9" t="n"/>
-      <c r="G74" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="H74" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="I74" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K74" s="34" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="18" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="O74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="34" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="Q74" s="18" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="R74" s="18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="S74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="34" t="n">
-        <v>2000.49</v>
-      </c>
-      <c r="V74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K74" s="9" t="n"/>
+      <c r="P74" s="9" t="n"/>
+      <c r="U74" s="9" t="n"/>
+      <c r="Z74" s="9" t="n"/>
       <c r="AB74" s="5" t="n"/>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -16759,78 +16634,78 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-70.17</v>
+        <v>-140.97</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>-62.91</v>
+        <v>-20143.71</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-2.47</v>
+        <v>-2866.12</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>0.65</v>
+        <v>-72.56</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>1.82</v>
+        <v>-71.97</v>
       </c>
       <c r="K75" s="34" t="n">
-        <v>-62.91</v>
+        <v>-23154.36</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>0</v>
+        <v>-74.09999999999999</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-5.33</v>
+        <v>-872.29</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-16.39</v>
+        <v>-90.48999999999999</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-20.65</v>
+        <v>-94.73999999999999</v>
       </c>
       <c r="P75" s="34" t="n">
-        <v>-42.37</v>
+        <v>-1131.62</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>-9.949999999999999</v>
+        <v>-84.05</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>-13.69</v>
+        <v>-4277.07</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>-19.27</v>
+        <v>-17779.98</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>-14.53</v>
+        <v>-2360.87</v>
       </c>
       <c r="U75" s="34" t="n">
-        <v>-57.44</v>
+        <v>-24501.97</v>
       </c>
       <c r="V75" s="18" t="n">
-        <v>-14.25</v>
+        <v>-88.95</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>-11.63</v>
+        <v>-5397.8</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>-10.24</v>
+        <v>577.76</v>
       </c>
       <c r="Y75" s="18" t="n">
         <v>-10.23</v>
       </c>
       <c r="Z75" s="34" t="n">
-        <v>-46.35</v>
+        <v>-4919.22</v>
       </c>
       <c r="AA75" s="18" t="n">
         <v>-10.01</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>-11.22</v>
+        <v>-5322.69</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -16852,41 +16727,73 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="9" t="n"/>
+      <c r="G76" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H76" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="I76" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K76" s="9" t="n"/>
+      <c r="K76" s="34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="18" t="n">
+        <v>2000</v>
+      </c>
       <c r="N76" s="18" t="n">
-        <v>0</v>
+        <v>124.99</v>
       </c>
       <c r="O76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P76" s="9" t="n"/>
+      <c r="P76" s="34" t="n">
+        <v>2124.99</v>
+      </c>
+      <c r="Q76" s="18" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>2000</v>
+      </c>
       <c r="S76" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U76" s="9" t="n"/>
+      <c r="U76" s="34" t="n">
+        <v>2000.49</v>
+      </c>
+      <c r="V76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="X76" s="18" t="n">
         <v>0</v>
       </c>
       <c r="Y76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n"/>
+      <c r="Z76" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="AB76" s="5" t="n"/>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -16908,12 +16815,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H77" s="18" t="n">
         <v>0</v>
@@ -16925,7 +16835,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="34" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="L77" s="18" t="n">
         <v>0</v>
@@ -16934,16 +16844,44 @@
         <v>0</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>0</v>
+        <v>124.99</v>
       </c>
       <c r="O77" s="18" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="34" t="n">
+        <v>124.99</v>
+      </c>
+      <c r="Q77" s="18" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S77" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U77" s="9" t="n"/>
-      <c r="Z77" s="9" t="n"/>
+      <c r="T77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="34" t="n">
+        <v>2000.49</v>
+      </c>
+      <c r="V77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="AB77" s="5" t="n"/>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -16965,61 +16903,78 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>-70.17</v>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="K78" s="9" t="n"/>
+      <c r="G78" s="18" t="n">
+        <v>-62.91</v>
+      </c>
+      <c r="H78" s="18" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="I78" s="18" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J78" s="18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K78" s="34" t="n">
+        <v>-62.91</v>
+      </c>
       <c r="L78" s="18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>0</v>
+        <v>-5.33</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>0</v>
+        <v>-16.39</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>0</v>
+        <v>-20.65</v>
       </c>
       <c r="P78" s="34" t="n">
-        <v>8.4</v>
+        <v>-42.37</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>0</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>0</v>
+        <v>-13.69</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>0</v>
+        <v>-19.27</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>0</v>
+        <v>-14.53</v>
       </c>
       <c r="U78" s="34" t="n">
-        <v>0</v>
+        <v>-57.44</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>208</v>
+        <v>-14.25</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>672</v>
+        <v>-11.63</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>103.5</v>
+        <v>-10.24</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>0</v>
+        <v>-10.23</v>
       </c>
       <c r="Z78" s="34" t="n">
-        <v>983.5</v>
+        <v>-46.35</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>0</v>
+        <v>-10.01</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>0</v>
+        <v>-11.22</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -17041,16 +16996,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
-        </is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="9" t="n"/>
+      <c r="I79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K79" s="9" t="n"/>
+      <c r="N79" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P79" s="9" t="n"/>
+      <c r="S79" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="T79" s="18" t="n">
-        <v>2271.64</v>
+        <v>0</v>
       </c>
       <c r="U79" s="9" t="n"/>
+      <c r="X79" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Y79" s="18" t="n">
         <v>0</v>
       </c>
@@ -17076,34 +17052,43 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
-      <c r="P80" s="9" t="n"/>
+      <c r="G80" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="U80" s="9" t="n"/>
-      <c r="V80" s="18" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="W80" s="18" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="34" t="n">
-        <v>171.2</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z80" s="9" t="n"/>
+      <c r="AB80" s="5" t="n"/>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -17124,33 +17109,61 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="K81" s="9" t="n"/>
-      <c r="P81" s="9" t="n"/>
-      <c r="U81" s="9" t="n"/>
+      <c r="L81" s="18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Q81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="34" t="n">
+        <v>0</v>
+      </c>
       <c r="V81" s="18" t="n">
-        <v>54892.54</v>
+        <v>208</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>-8558.57</v>
+        <v>672</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>3281.58</v>
+        <v>103.5</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>6200.66</v>
+        <v>0</v>
       </c>
       <c r="Z81" s="34" t="n">
-        <v>55816.21</v>
+        <v>983.5</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>63726.93</v>
+        <v>0</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>2046.77</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -17172,26 +17185,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>자기주식의취득</t>
         </is>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="K82" s="9" t="n"/>
       <c r="P82" s="9" t="n"/>
+      <c r="T82" s="18" t="n">
+        <v>2271.64</v>
+      </c>
       <c r="U82" s="9" t="n"/>
-      <c r="X82" s="18" t="n">
-        <v>2904.46</v>
-      </c>
       <c r="Y82" s="18" t="n">
-        <v>6100.97</v>
+        <v>0</v>
       </c>
       <c r="Z82" s="9" t="n"/>
-      <c r="AA82" s="18" t="n">
-        <v>6299.96</v>
-      </c>
-      <c r="AB82" s="19" t="n">
-        <v>1688.79</v>
-      </c>
+      <c r="AB82" s="5" t="n"/>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
       <c r="AE82" s="11" t="n"/>
@@ -17205,6 +17213,142 @@
       <c r="AM82" s="10" t="n"/>
       <c r="AN82" s="10" t="n"/>
       <c r="AO82" s="11" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="n"/>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
+      <c r="V83" s="18" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="W83" s="18" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="X83" s="18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Y83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="34" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="AA83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="11" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="11" t="n"/>
+      <c r="AK83" s="10" t="n"/>
+      <c r="AL83" s="10" t="n"/>
+      <c r="AM83" s="10" t="n"/>
+      <c r="AN83" s="10" t="n"/>
+      <c r="AO83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="U84" s="9" t="n"/>
+      <c r="V84" s="18" t="n">
+        <v>54892.54</v>
+      </c>
+      <c r="W84" s="18" t="n">
+        <v>-8558.57</v>
+      </c>
+      <c r="X84" s="18" t="n">
+        <v>3281.58</v>
+      </c>
+      <c r="Y84" s="18" t="n">
+        <v>6200.66</v>
+      </c>
+      <c r="Z84" s="34" t="n">
+        <v>55816.21</v>
+      </c>
+      <c r="AA84" s="18" t="n">
+        <v>63726.93</v>
+      </c>
+      <c r="AB84" s="19" t="n">
+        <v>2046.77</v>
+      </c>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="11" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="11" t="n"/>
+      <c r="AK84" s="10" t="n"/>
+      <c r="AL84" s="10" t="n"/>
+      <c r="AM84" s="10" t="n"/>
+      <c r="AN84" s="10" t="n"/>
+      <c r="AO84" s="11" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
+      <c r="X85" s="18" t="n">
+        <v>2904.46</v>
+      </c>
+      <c r="Y85" s="18" t="n">
+        <v>6100.97</v>
+      </c>
+      <c r="Z85" s="9" t="n"/>
+      <c r="AA85" s="18" t="n">
+        <v>6299.96</v>
+      </c>
+      <c r="AB85" s="19" t="n">
+        <v>1688.79</v>
+      </c>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="11" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="11" t="n"/>
+      <c r="AK85" s="10" t="n"/>
+      <c r="AL85" s="10" t="n"/>
+      <c r="AM85" s="10" t="n"/>
+      <c r="AN85" s="10" t="n"/>
+      <c r="AO85" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17465,7 +17609,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>30650</v>
+        <v>30150</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>22550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>30300</v>
+        <v>29700</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>30875</v>
+        <v>30633.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>30650</v>
+        <v>30150</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05426817893620568</v>
+        <v>0.05426817893620548</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02023888886218658</v>
+        <v>0.02023888886217404</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.67</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>30150</v>
+        <v>29450</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>22550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>29700</v>
+        <v>29300</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>30633.3</v>
+        <v>30375</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>30150</v>
+        <v>29450</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 30,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 30,450원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.32</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>29450</v>
+        <v>28800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>22550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>29300</v>
+        <v>28200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>30375</v>
+        <v>30040</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>29450</v>
+        <v>28800</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 30,450원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 30,000원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.82</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05426817893620548</v>
+        <v>0.05426817893620568</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02023888886217404</v>
+        <v>0.02023888886218658</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>28800</v>
+        <v>28850</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>30040</v>
+        <v>30050</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>28800</v>
+        <v>28850</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 30,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 29,400원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.05426817893620568</v>
+        <v>0.05426817893620548</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.02023888886218658</v>
+        <v>0.02023888886217404</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.36</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>28850</v>
+        <v>27500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>22550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>28200</v>
+        <v>27350</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>30050</v>
+        <v>29625</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>28850</v>
+        <v>27500</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.4</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>27500</v>
+        <v>27200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>22550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>27350</v>
+        <v>26050</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>29625</v>
+        <v>29257.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>27500</v>
+        <v>27200</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 29,400원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 28,700원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.44</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>27200</v>
+        <v>28800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>29257.1</v>
+        <v>29206.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>27200</v>
+        <v>28800</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 28,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 27,600원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.23</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>28800</v>
+        <v>28000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>29206.2</v>
+        <v>28636.4</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>28800</v>
+        <v>28000</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 27,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,700원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.36</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/014620_model.xlsx
+++ b/argus/kship/models/014620_model.xlsx
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>31550</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>28000</v>
+        <v>25600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>22550</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>26050</v>
+        <v>25450</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>28438.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>28636.4</v>
+        <v>27968.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>28000</v>
+        <v>25600</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 26,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 27,300원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34873,7 +34873,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36881,7 +36881,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="32">
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="33">
